--- a/documents/TD2/TD2_corrige.xlsx
+++ b/documents/TD2/TD2_corrige.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/04994f5a795f6aab/Doc enseignement/Université Paris1 Panthéon-Sorbonne/Année 2025-2026/TD2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="419" documentId="11_815ADB0CADF006AE32FE069F16FEA8C829E5B77F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CFFE974-D7C2-402F-A0CA-40A4B17364B4}"/>
+  <xr:revisionPtr revIDLastSave="431" documentId="11_815ADB0CADF006AE32FE069F16FEA8C829E5B77F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02E235AD-AE9D-4922-B85D-5E302E267F2A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1731,15 +1731,6 @@
     <t>En Chine, les valeurs élevées s'expliquent par la taille énorme de la population et par des estimations issues de modèles tenant compte de la sous-déclaration, de l'âge moyen élevé et de dépistages moins fréquents. Les données restent donc incertaines ou parfois sous-estimées.</t>
   </si>
   <si>
-    <t>Pour ces îles, les estimations sont souvent très faibles et variables. Cela s'explique par :
-•	leur faible ou petite population,
-•	des modèles statistiques qui sont moins précis sur de petits territoires,
-•	la variabilité annuelle ou du sous-diagnostic (moins de dépistage, infrastructures limitées).</t>
-  </si>
-  <si>
-    <t>Ces îles françaises, comme les Caraïbes, ont une proportion de populations d'origine africaine, historiquement associée à une incidence plus élevée du cancer de la prostate. Cependant, leurs systèmes de santé sont bien développés comparés aux petites îles. On peut donc déduire que les chiffres seront plus élevés que la métropole, mais plus fiables et relativement mieux surveillés, avec des taux d'incidence proches des autres îles à population comparable.</t>
-  </si>
-  <si>
     <t>Voir Exercice F4</t>
   </si>
   <si>
@@ -1749,6 +1740,19 @@
   </si>
   <si>
     <t>Voir Exercice F4- Carto</t>
+  </si>
+  <si>
+    <t>Pour ces îles, les estimations sont souvent très faibles et variables. Plusieurs éléments peuvent contribuer à expliquer cette situation :
+ - leur faible population, qui rend les indicateurs statistiques plus sensibles à de petites variations du nombre de cas ;
+  - des estimations statistiques potentiellement moins précises pour les territoires de petite taille ;
+  - la variabilité annuelle, ainsi que d'éventuelles différences dans le dépistage, le diagnostic et l'accès aux infrastructures de santé ;
+  -  l'exposition historique de certaines populations des Antilles et des Caraïbes à des pesticides utilisés dans les cultures, notamment dans la production de bananes. Certains de ces produits ont été étudiés en raison de leurs effets potentiels sur la santé et de leur possible association avec le risque de cancer de la prostate. Cette exposition peut donc être évoquée comme une hypothèse supplémentaire à examiner, sans pour autant permettre, à partir de ces seules données, d'établir une relation causale entre l'utilisation de ces produits et les niveaux de cancer de la prostate observés dans chaque île.</t>
+  </si>
+  <si>
+    <t>Cas particulier des îles françaises des Antilles (Guadeloupe et Martinique)
+Pour la Guadeloupe et la Martinique, une hypothèse supplémentaire peut être avancée. Ces territoires ont connu une exposition importante au chlordécone, pesticide utilisé pendant plusieurs années dans les bananeraies. Des travaux scientifiques ont étudié le lien entre cette exposition et le risque de cancer de la prostate.
+Ainsi, si les données montrent une situation particulière de la Guadeloupe ou de la Martinique concernant le cancer de la prostate, l'exposition au chlordécone constitue un facteur explicatif potentiel à prendre en compte. Toutefois, les données statistiques présentées ici ne suffisent pas, à elles seules, à démontrer que le chlordécone est la cause des niveaux observés. D'autres facteurs peuvent également intervenir, notamment la structure par âge de la population, le dépistage, l'accès aux soins ou d'autres caractéristiques de la population.
+Ce cas illustre donc une distinction essentielle en statistique : observer une association ne permet pas, à lui seul, d'établir une relation de causalité.</t>
   </si>
 </sst>
 </file>
@@ -2214,12 +2218,6 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2227,6 +2225,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -13840,6 +13844,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
@@ -14188,7 +14196,7 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D6" s="51" t="s">
+      <c r="D6" s="54" t="s">
         <v>554</v>
       </c>
     </row>
@@ -14196,94 +14204,94 @@
       <c r="A7" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="51"/>
+      <c r="D7" s="54"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D8" s="51"/>
+      <c r="D8" s="54"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D9" s="51"/>
+      <c r="D9" s="54"/>
     </row>
     <row r="11" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F11" s="55" t="s">
+      <c r="F11" s="53" t="s">
         <v>540</v>
       </c>
-      <c r="G11" s="55"/>
-      <c r="H11" s="55"/>
-      <c r="I11" s="55"/>
-      <c r="J11" s="55"/>
-      <c r="K11" s="55"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="53"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="53"/>
+      <c r="K11" s="53"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="55"/>
-      <c r="K12" s="55"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="53"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F13" s="55"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="55"/>
-      <c r="J13" s="55"/>
-      <c r="K13" s="55"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="53"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="53"/>
+      <c r="K13" s="53"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F14" s="55"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="55"/>
-      <c r="I14" s="55"/>
-      <c r="J14" s="55"/>
-      <c r="K14" s="55"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="53"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F15" s="55"/>
-      <c r="G15" s="55"/>
-      <c r="H15" s="55"/>
-      <c r="I15" s="55"/>
-      <c r="J15" s="55"/>
-      <c r="K15" s="55"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="53"/>
+      <c r="K15" s="53"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F16" s="55"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="55"/>
-      <c r="I16" s="55"/>
-      <c r="J16" s="55"/>
-      <c r="K16" s="55"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="53"/>
+      <c r="H16" s="53"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="53"/>
+      <c r="K16" s="53"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="55"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="55"/>
-      <c r="I17" s="55"/>
-      <c r="J17" s="55"/>
-      <c r="K17" s="55"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="53"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="53"/>
+      <c r="K17" s="53"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F18" s="55"/>
-      <c r="G18" s="55"/>
-      <c r="H18" s="55"/>
-      <c r="I18" s="55"/>
-      <c r="J18" s="55"/>
-      <c r="K18" s="55"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="53"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="53"/>
+      <c r="K18" s="53"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B19" s="6"/>
@@ -14293,12 +14301,12 @@
       <c r="D19" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F19" s="55"/>
-      <c r="G19" s="55"/>
-      <c r="H19" s="55"/>
-      <c r="I19" s="55"/>
-      <c r="J19" s="55"/>
-      <c r="K19" s="55"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="53"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="53"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
@@ -14306,12 +14314,12 @@
       </c>
       <c r="C20" s="10"/>
       <c r="D20" s="11"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="55"/>
-      <c r="H20" s="55"/>
-      <c r="I20" s="55"/>
-      <c r="J20" s="55"/>
-      <c r="K20" s="55"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="53"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
@@ -14319,12 +14327,12 @@
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="11"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="55"/>
-      <c r="H21" s="55"/>
-      <c r="I21" s="55"/>
-      <c r="J21" s="55"/>
-      <c r="K21" s="55"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="53"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B22" s="12" t="s">
@@ -14332,12 +14340,12 @@
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="14"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="55"/>
-      <c r="I22" s="55"/>
-      <c r="J22" s="55"/>
-      <c r="K22" s="55"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="53"/>
     </row>
     <row r="27" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
@@ -14358,92 +14366,92 @@
       <c r="A32" s="45" t="s">
         <v>548</v>
       </c>
-      <c r="E32" s="51" t="s">
+      <c r="E32" s="54" t="s">
         <v>553</v>
       </c>
-      <c r="F32" s="51"/>
-      <c r="G32" s="51"/>
-      <c r="H32" s="51"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="54"/>
     </row>
     <row r="33" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="E33" s="51"/>
-      <c r="F33" s="51"/>
-      <c r="G33" s="51"/>
-      <c r="H33" s="51"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="54"/>
     </row>
     <row r="34" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="E34" s="51" t="s">
+      <c r="E34" s="54" t="s">
         <v>555</v>
       </c>
-      <c r="F34" s="51"/>
-      <c r="G34" s="51"/>
-      <c r="H34" s="51"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="54"/>
     </row>
     <row r="35" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="E35" s="51"/>
-      <c r="F35" s="51"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="51"/>
+      <c r="E35" s="54"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="54"/>
     </row>
     <row r="36" spans="1:11" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="51"/>
+      <c r="E36" s="54"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="54"/>
     </row>
     <row r="37" spans="1:11" ht="59.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E37" s="52" t="s">
+      <c r="E37" s="55" t="s">
         <v>556</v>
       </c>
-      <c r="F37" s="52"/>
-      <c r="G37" s="52"/>
-      <c r="H37" s="52"/>
-      <c r="I37" s="52"/>
-      <c r="J37" s="52"/>
-      <c r="K37" s="52"/>
-    </row>
-    <row r="38" spans="1:11" ht="73.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F37" s="55"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="55"/>
+      <c r="J37" s="55"/>
+      <c r="K37" s="55"/>
+    </row>
+    <row r="38" spans="1:11" ht="210" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="E38" s="53" t="s">
-        <v>557</v>
-      </c>
-      <c r="F38" s="54"/>
-      <c r="G38" s="54"/>
-      <c r="H38" s="54"/>
-      <c r="I38" s="54"/>
-      <c r="J38" s="54"/>
-      <c r="K38" s="54"/>
-    </row>
-    <row r="39" spans="1:11" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E38" s="51" t="s">
+        <v>560</v>
+      </c>
+      <c r="F38" s="52"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="52"/>
+      <c r="K38" s="52"/>
+    </row>
+    <row r="39" spans="1:11" ht="223.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="E39" s="53" t="s">
-        <v>558</v>
-      </c>
-      <c r="F39" s="53"/>
-      <c r="G39" s="53"/>
-      <c r="H39" s="53"/>
-      <c r="I39" s="53"/>
-      <c r="J39" s="53"/>
-      <c r="K39" s="53"/>
+      <c r="E39" s="51" t="s">
+        <v>561</v>
+      </c>
+      <c r="F39" s="51"/>
+      <c r="G39" s="51"/>
+      <c r="H39" s="51"/>
+      <c r="I39" s="51"/>
+      <c r="J39" s="51"/>
+      <c r="K39" s="51"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="16"/>
@@ -14468,58 +14476,58 @@
       <c r="A47" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E47" s="51" t="s">
-        <v>559</v>
-      </c>
-      <c r="F47" s="51"/>
-      <c r="G47" s="51"/>
-      <c r="H47" s="51"/>
-      <c r="I47" s="51"/>
-      <c r="J47" s="51"/>
+      <c r="E47" s="54" t="s">
+        <v>557</v>
+      </c>
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="54"/>
+      <c r="I47" s="54"/>
+      <c r="J47" s="54"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E48" s="51"/>
-      <c r="F48" s="51"/>
-      <c r="G48" s="51"/>
-      <c r="H48" s="51"/>
-      <c r="I48" s="51"/>
-      <c r="J48" s="51"/>
+      <c r="E48" s="54"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="54"/>
+      <c r="J48" s="54"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E49" s="51"/>
-      <c r="F49" s="51"/>
-      <c r="G49" s="51"/>
-      <c r="H49" s="51"/>
-      <c r="I49" s="51"/>
-      <c r="J49" s="51"/>
+      <c r="E49" s="54"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="54"/>
+      <c r="I49" s="54"/>
+      <c r="J49" s="54"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E50" s="51"/>
-      <c r="F50" s="51"/>
-      <c r="G50" s="51"/>
-      <c r="H50" s="51"/>
-      <c r="I50" s="51"/>
-      <c r="J50" s="51"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="54"/>
+      <c r="I50" s="54"/>
+      <c r="J50" s="54"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E51" s="51"/>
-      <c r="F51" s="51"/>
-      <c r="G51" s="51"/>
-      <c r="H51" s="51"/>
-      <c r="I51" s="51"/>
-      <c r="J51" s="51"/>
+      <c r="E51" s="54"/>
+      <c r="F51" s="54"/>
+      <c r="G51" s="54"/>
+      <c r="H51" s="54"/>
+      <c r="I51" s="54"/>
+      <c r="J51" s="54"/>
     </row>
     <row r="52" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E52" s="47"/>
@@ -14530,11 +14538,11 @@
       <c r="J52" s="47"/>
     </row>
     <row r="53" spans="1:10" ht="46.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="53" t="s">
-        <v>560</v>
-      </c>
-      <c r="B53" s="54"/>
-      <c r="C53" s="54"/>
+      <c r="A53" s="51" t="s">
+        <v>558</v>
+      </c>
+      <c r="B53" s="52"/>
+      <c r="C53" s="52"/>
       <c r="E53" s="47"/>
       <c r="F53" s="47"/>
       <c r="G53" s="47"/>
@@ -14707,8 +14715,8 @@
       <c r="A80" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D80" s="51" t="s">
-        <v>561</v>
+      <c r="D80" s="54" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -14718,7 +14726,7 @@
       <c r="B81" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D81" s="51"/>
+      <c r="D81" s="54"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
@@ -14727,7 +14735,7 @@
       <c r="B82" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D82" s="51"/>
+      <c r="D82" s="54"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
@@ -14736,7 +14744,7 @@
       <c r="B83" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D83" s="51"/>
+      <c r="D83" s="54"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
@@ -14745,10 +14753,10 @@
       <c r="B84" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D84" s="51"/>
+      <c r="D84" s="54"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D85" s="51"/>
+      <c r="D85" s="54"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
@@ -14757,19 +14765,19 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="D80:D85"/>
+    <mergeCell ref="E37:K37"/>
+    <mergeCell ref="E38:K38"/>
+    <mergeCell ref="E39:K39"/>
+    <mergeCell ref="E47:J51"/>
     <mergeCell ref="A53:C53"/>
     <mergeCell ref="F11:K22"/>
     <mergeCell ref="D6:D9"/>
     <mergeCell ref="E32:H33"/>
     <mergeCell ref="E34:H36"/>
-    <mergeCell ref="D80:D85"/>
-    <mergeCell ref="E37:K37"/>
-    <mergeCell ref="E38:K38"/>
-    <mergeCell ref="E39:K39"/>
-    <mergeCell ref="E47:J51"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -28984,11 +28992,11 @@
         <v>69.919536000000008</v>
       </c>
       <c r="F203" s="44">
-        <f t="shared" ref="F203:F234" si="18">D203-E203</f>
+        <f t="shared" ref="F203:F207" si="18">D203-E203</f>
         <v>-4.2945360000000079</v>
       </c>
       <c r="G203" s="46">
-        <f t="shared" ref="G203:G234" si="19">F203/E203</f>
+        <f t="shared" ref="G203:G207" si="19">F203/E203</f>
         <v>-6.1421116982240946E-2</v>
       </c>
     </row>
